--- a/employee_enrollment_forms/031_hmo_enrollment_field_office_i_dependent--employee_enrollment_forms.xlsx
+++ b/employee_enrollment_forms/031_hmo_enrollment_field_office_i_dependent--employee_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'dependent'}</t>
+          <t>dependent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Dependent'}</t>
+          <t>Dependent</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'hmo'}</t>
+          <t>hmo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'HMO'}</t>
+          <t>HMO</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'ppo'}</t>
+          <t>ppo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'PPO'}</t>
+          <t>PPO</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'pos'}</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'POS'}</t>
+          <t>POS</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
